--- a/backend/src/db/demo-docs/measurements-cuffed-joggers.xlsx
+++ b/backend/src/db/demo-docs/measurements-cuffed-joggers.xlsx
@@ -589,19 +589,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>34.5</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>41</v>
       </c>
     </row>
@@ -618,19 +621,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>53</v>
       </c>
     </row>
@@ -647,19 +653,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -772,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>32.5</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>34.5</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>39</v>
       </c>
     </row>
@@ -801,19 +813,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>11.5</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>13.5</v>
       </c>
     </row>
@@ -990,19 +1005,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="F23" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>13.5</v>
       </c>
     </row>
@@ -1019,19 +1037,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="G24" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>15.5</v>
       </c>
     </row>
